--- a/fhir/CodeSystem-participant-function.xlsx
+++ b/fhir/CodeSystem-participant-function.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -151,6 +151,42 @@
   </si>
   <si>
     <t>Default careteam for task and communication</t>
+  </si>
+  <si>
+    <t>administrative</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>Participant has administrative function of maintaining EpisodeOfCare and/or CarePlan</t>
+  </si>
+  <si>
+    <t>monitoring</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Participant monitors Patient's submissions and adherence to plan</t>
+  </si>
+  <si>
+    <t>supporting</t>
+  </si>
+  <si>
+    <t>Supporting</t>
+  </si>
+  <si>
+    <t>Participant supports other participants, for instance by setting up and adjusting EpisodeOfCare and/or CarePlan</t>
+  </si>
+  <si>
+    <t>informed</t>
+  </si>
+  <si>
+    <t>Informed</t>
+  </si>
+  <si>
+    <t>Participant is involved to stay informed and expected to perform few if any actions</t>
   </si>
 </sst>
 </file>
@@ -456,7 +492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -515,6 +551,62 @@
         <v>45</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/fhir/CodeSystem-participant-function.xlsx
+++ b/fhir/CodeSystem-participant-function.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-participant-function.xlsx
+++ b/fhir/CodeSystem-participant-function.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-participant-function.xlsx
+++ b/fhir/CodeSystem-participant-function.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-participant-function.xlsx
+++ b/fhir/CodeSystem-participant-function.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-participant-function.xlsx
+++ b/fhir/CodeSystem-participant-function.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-participant-function.xlsx
+++ b/fhir/CodeSystem-participant-function.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
